--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T16:33:35+00:00</t>
+    <t>2025-04-24T12:56:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1470,17 +1470,17 @@
   <dimension ref="A1:AN41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="29.6328125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="26.87890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.2578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="25.40625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="23.04296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.9375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="108.42578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="92.95703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1489,26 +1489,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="17.79296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.54296875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="15.25390625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="45.90234375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="76.3359375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="185.94140625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="35.76171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="65.4453125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="159.4140625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="30.66015625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:56:51+00:00</t>
+    <t>2025-04-24T12:57:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:57:11+00:00</t>
+    <t>2025-04-24T13:09:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T13:09:23+00:00</t>
+    <t>2025-04-29T14:26:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T14:28:01+00:00</t>
+    <t>2026-03-04T14:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T14:06:01+00:00</t>
+    <t>2026-03-04T14:38:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T14:38:02+00:00</t>
+    <t>2026-03-04T16:46:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="361">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T16:46:41+00:00</t>
+    <t>2026-05-06T07:19:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -240,13 +240,13 @@
     <t>Mapping: Spécification métier vers le profil PDSm_FolderComprehensive</t>
   </si>
   <si>
+    <t>Mapping: XDS and MHD Mapping</t>
+  </si>
+  <si>
     <t>Mapping: RIM Mapping</t>
   </si>
   <si>
     <t>Mapping: FiveWs Pattern Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: XDS and MHD Mapping</t>
   </si>
   <si>
     <t>Collection
@@ -279,10 +279,10 @@
     <t>Classeur</t>
   </si>
   <si>
+    <t>XDS Folder: Used in the context of the IHE MHD ImplementationGuide</t>
+  </si>
+  <si>
     <t>Act[classCode&lt;ORG,moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>XDS Folder</t>
   </si>
   <si>
     <t>List.id</t>
@@ -443,7 +443,7 @@
     <t>List.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -484,7 +484,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -508,7 +508,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -551,7 +551,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -667,13 +667,13 @@
 </t>
   </si>
   <si>
+    <t>Folder.entryUUID and Folder.uniqueId</t>
+  </si>
+  <si>
     <t>.id</t>
   </si>
   <si>
     <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>Folder.entryUUID and Folder.uniqueId</t>
   </si>
   <si>
     <t>List.identifier:uniqueId</t>
@@ -689,13 +689,7 @@
     <t>Identifiant unique du classeur attribué par le système initiateur.</t>
   </si>
   <si>
-    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
-  </si>
-  <si>
     <t>idUnique : [0..*] Identifiant</t>
-  </si>
-  <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>List.identifier:entryUUID</t>
@@ -735,15 +729,15 @@
     <t>statut : [1..1] Code</t>
   </si>
   <si>
+    <t>Folder.availabilityStatus</t>
+  </si>
+  <si>
     <t>.status[current=active;retired=obsolete;entered-in-error=nullified]</t>
   </si>
   <si>
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>Folder.availabilityStatus</t>
-  </si>
-  <si>
     <t>List.mode</t>
   </si>
   <si>
@@ -768,15 +762,15 @@
     <t>http://hl7.org/fhir/ValueSet/list-mode|4.0.1</t>
   </si>
   <si>
+    <t>shall be 'working'</t>
+  </si>
+  <si>
     <t>.outBoundRelationship[typeCode=COMP].target[classCode=OBS"].value</t>
   </si>
   <si>
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>shall be 'working'</t>
-  </si>
-  <si>
     <t>List.title</t>
   </si>
   <si>
@@ -795,10 +789,10 @@
     <t>titreClasseur : [0..1] Texte</t>
   </si>
   <si>
+    <t>Folder.title</t>
+  </si>
+  <si>
     <t>.title</t>
-  </si>
-  <si>
-    <t>Folder.title</t>
   </si>
   <si>
     <t>List.code</t>
@@ -831,13 +825,13 @@
     <t>https://profiles.ihe.net/ITI/MHD/ValueSet/MHDlistTypesVS</t>
   </si>
   <si>
+    <t>shall be 'folder'</t>
+  </si>
+  <si>
     <t>.code</t>
   </si>
   <si>
     <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>shall be 'folder'</t>
   </si>
   <si>
     <t>List.subject</t>
@@ -862,19 +856,19 @@
     <t>idPatient : [0..1] Identifiant</t>
   </si>
   <si>
+    <t>Folder.patientId</t>
+  </si>
+  <si>
     <t>.participation[typeCode&lt;SUB].role (and sometimes .player)</t>
   </si>
   <si>
     <t>FiveWs.subject</t>
   </si>
   <si>
-    <t>Folder.patientId</t>
-  </si>
-  <si>
     <t>List.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -912,13 +906,13 @@
     <t>derniereMiseAJour : [0..1] DateHeure</t>
   </si>
   <si>
+    <t>Folder.lastUpdateTime</t>
+  </si>
+  <si>
     <t>.participation[typeCode&lt;AUT].time[type=TS]</t>
   </si>
   <si>
     <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>Folder.lastUpdateTime</t>
   </si>
   <si>
     <t>List.source</t>
@@ -928,7 +922,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|Device)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -968,7 +962,7 @@
     <t>What order applies to the items in a list.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-order</t>
+    <t>http://hl7.org/fhir/ValueSet/list-order|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].sequenceNumber &gt; 1</t>
@@ -987,10 +981,10 @@
     <t>Comments that apply to the overall list.</t>
   </si>
   <si>
+    <t>Folder.comments</t>
+  </si>
+  <si>
     <t>.inboundRelationship[typeCode=SUBJ].act.text</t>
-  </si>
-  <si>
-    <t>Folder.comments</t>
   </si>
   <si>
     <t>List.entry</t>
@@ -1060,7 +1054,7 @@
     <t>Codes that provide further information about the reason and meaning of the item in the list.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-item-flag</t>
+    <t>http://hl7.org/fhir/ValueSet/list-item-flag|4.0.1</t>
   </si>
   <si>
     <t>List.entry.deleted</t>
@@ -1123,12 +1117,12 @@
     <t>listeFiches : [0..*] Identifiant</t>
   </si>
   <si>
+    <t>references to DocumentReference(s)</t>
+  </si>
+  <si>
     <t>.target or .role or .role.entity</t>
   </si>
   <si>
-    <t>references to DocumentReference(s)</t>
-  </si>
-  <si>
     <t>List.emptyReason</t>
   </si>
   <si>
@@ -1147,7 +1141,7 @@
     <t>If a list is empty, why it is empty.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-empty-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/list-empty-reason|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>
@@ -1506,9 +1500,9 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="65.4453125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="159.4140625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="30.66015625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="56.09375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="159.4140625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1739,10 +1733,10 @@
         <v>86</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" hidden="true">
@@ -2074,10 +2068,10 @@
         <v>80</v>
       </c>
       <c r="AL5" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM5" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="AM5" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>80</v>
@@ -2188,10 +2182,10 @@
         <v>80</v>
       </c>
       <c r="AL6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM6" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="AM6" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>80</v>
@@ -2644,13 +2638,13 @@
         <v>80</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>142</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" hidden="true">
@@ -3214,10 +3208,10 @@
         <v>80</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>80</v>
@@ -3328,10 +3322,10 @@
         <v>80</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>80</v>
@@ -3819,7 +3813,7 @@
         <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3879,33 +3873,33 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>217</v>
+        <v>80</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>80</v>
+        <v>209</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>80</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>203</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>80</v>
@@ -3927,13 +3921,13 @@
         <v>80</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3993,7 +3987,7 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>101</v>
@@ -4002,21 +3996,21 @@
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>217</v>
+        <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>80</v>
+        <v>209</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>80</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4042,13 +4036,13 @@
         <v>166</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4074,14 +4068,14 @@
         <v>80</v>
       </c>
       <c r="X23" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="Z23" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="Y23" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>228</v>
-      </c>
       <c r="AA23" t="s" s="2">
         <v>80</v>
       </c>
@@ -4098,7 +4092,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>89</v>
@@ -4113,24 +4107,24 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>232</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4156,16 +4150,16 @@
         <v>166</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4175,29 +4169,29 @@
         <v>80</v>
       </c>
       <c r="S24" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="T24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X24" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>240</v>
-      </c>
       <c r="AA24" t="s" s="2">
         <v>80</v>
       </c>
@@ -4214,7 +4208,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>89</v>
@@ -4232,21 +4226,21 @@
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>243</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4272,14 +4266,14 @@
         <v>103</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4292,7 +4286,7 @@
         <v>80</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>80</v>
@@ -4328,7 +4322,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4343,24 +4337,24 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AN25" t="s" s="2">
-        <v>251</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4383,19 +4377,19 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -4405,7 +4399,7 @@
         <v>80</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>80</v>
@@ -4420,11 +4414,11 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
@@ -4442,7 +4436,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4460,21 +4454,21 @@
         <v>80</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>262</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4497,19 +4491,19 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -4558,7 +4552,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4573,24 +4567,24 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>272</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4613,13 +4607,13 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4670,7 +4664,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4688,21 +4682,21 @@
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>277</v>
+        <v>107</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>107</v>
+        <v>276</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4725,19 +4719,19 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -4786,7 +4780,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4801,28 +4795,28 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>288</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4841,19 +4835,19 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>80</v>
@@ -4902,7 +4896,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4920,21 +4914,21 @@
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>296</v>
+        <v>107</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>107</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4957,19 +4951,19 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -4997,10 +4991,10 @@
         <v>170</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5018,7 +5012,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5036,21 +5030,21 @@
         <v>80</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>305</v>
+        <v>107</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>80</v>
+        <v>303</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>107</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5073,13 +5067,13 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5130,7 +5124,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5148,21 +5142,21 @@
         <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>80</v>
+        <v>309</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>311</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5185,16 +5179,16 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5244,7 +5238,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5253,7 +5247,7 @@
         <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>101</v>
@@ -5262,10 +5256,10 @@
         <v>80</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>318</v>
+        <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>80</v>
+        <v>316</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -5273,10 +5267,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5374,10 +5368,10 @@
         <v>80</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
@@ -5385,10 +5379,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5488,10 +5482,10 @@
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -5499,14 +5493,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5528,16 +5522,16 @@
         <v>110</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -5586,7 +5580,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5604,10 +5598,10 @@
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
@@ -5615,10 +5609,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5641,19 +5635,19 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -5681,10 +5675,10 @@
         <v>156</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -5702,7 +5696,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5720,21 +5714,21 @@
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>241</v>
+        <v>107</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>107</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5757,26 +5751,26 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="P38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q38" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="O38" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="P38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q38" t="s" s="2">
-        <v>340</v>
-      </c>
       <c r="R38" t="s" s="2">
         <v>80</v>
       </c>
@@ -5820,7 +5814,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5829,7 +5823,7 @@
         <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>101</v>
@@ -5838,21 +5832,21 @@
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>342</v>
+        <v>107</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>80</v>
+        <v>340</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>107</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5875,17 +5869,17 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -5934,7 +5928,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5952,21 +5946,21 @@
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>347</v>
+        <v>107</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>80</v>
+        <v>345</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>107</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5989,13 +5983,13 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6046,7 +6040,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>89</v>
@@ -6061,24 +6055,24 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AL40" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AN40" t="s" s="2">
-        <v>354</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6101,19 +6095,19 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6141,10 +6135,10 @@
         <v>170</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>80</v>
@@ -6162,7 +6156,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6171,7 +6165,7 @@
         <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>101</v>
@@ -6180,13 +6174,13 @@
         <v>80</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>362</v>
+        <v>107</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>80</v>
+        <v>360</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>107</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:19:11+00:00</t>
+    <t>2026-05-27T14:14:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:14:06+00:00</t>
+    <t>2026-05-28T14:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:04:20+00:00</t>
+    <t>2026-05-28T14:30:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:30:01+00:00</t>
+    <t>2026-06-03T13:49:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T13:49:29+00:00</t>
+    <t>2026-06-03T13:50:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T13:50:50+00:00</t>
+    <t>2026-06-30T13:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T13:26:19+00:00</t>
+    <t>2026-06-30T13:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T13:34:41+00:00</t>
+    <t>2026-06-30T16:19:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T16:19:40+00:00</t>
+    <t>2026-07-15T16:15:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T16:15:50+00:00</t>
+    <t>2026-07-27T15:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:55:54+00:00</t>
+    <t>2026-08-06T13:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:06:39+00:00</t>
+    <t>2026-08-06T14:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T14:18:59+00:00</t>
+    <t>2026-08-06T14:57:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
